--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128260561</v>
+        <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>91680</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667956</v>
+        <v>668216</v>
       </c>
       <c r="R4" t="n">
-        <v>6691635</v>
+        <v>6691659</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,6 +985,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1000,16 +1015,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260561</t>
+          <t>https://artportalen.se/Sighting/136824213</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128260554</v>
+        <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>93209</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668031</v>
+        <v>668343</v>
       </c>
       <c r="R5" t="n">
-        <v>6691632</v>
+        <v>6691845</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1086,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På bark som hänger från lågan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,6 +1107,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1102,16 +1137,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260554</t>
+          <t>https://artportalen.se/Sighting/136824809</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128260556</v>
+        <v>136824222</v>
       </c>
       <c r="B6" t="n">
-        <v>93209</v>
+        <v>83343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1154,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668353</v>
+        <v>668057</v>
       </c>
       <c r="R6" t="n">
-        <v>6691720</v>
+        <v>6691608</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1211,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal senvuxen gran med grov bark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,8 +1230,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1204,54 +1263,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260556</t>
+          <t>https://artportalen.se/Sighting/136824222</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128344128</v>
+        <v>128260561</v>
       </c>
       <c r="B7" t="n">
-        <v>93209</v>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668138</v>
+        <v>667956</v>
       </c>
       <c r="R7" t="n">
-        <v>6691627</v>
+        <v>6691635</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,27 +1354,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344128</t>
+          <t>https://artportalen.se/Sighting/128260561</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127382963</v>
+        <v>136824227</v>
       </c>
       <c r="B8" t="n">
-        <v>93215</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,13 +1406,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668299</v>
+        <v>668027</v>
       </c>
       <c r="R8" t="n">
-        <v>6691892</v>
+        <v>6691562</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,12 +1436,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,51 +1472,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382963</t>
+          <t>https://artportalen.se/Sighting/136824227</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128344126</v>
+        <v>136824228</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668368</v>
+        <v>668033</v>
       </c>
       <c r="R9" t="n">
-        <v>6691735</v>
+        <v>6691587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,12 +1543,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,65 +1568,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344126</t>
+          <t>https://artportalen.se/Sighting/136824228</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125807856</v>
+        <v>136824229</v>
       </c>
       <c r="B10" t="n">
-        <v>91872</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668270</v>
+        <v>668276</v>
       </c>
       <c r="R10" t="n">
-        <v>6691807</v>
+        <v>6691689</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,12 +1650,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,16 +1686,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807856</t>
+          <t>https://artportalen.se/Sighting/136824229</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128260536</v>
+        <v>128260554</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668066</v>
+        <v>668031</v>
       </c>
       <c r="R11" t="n">
-        <v>6691644</v>
+        <v>6691632</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1700,21 +1774,6 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1729,54 +1788,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260536</t>
+          <t>https://artportalen.se/Sighting/128260554</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125853668</v>
+        <v>128260556</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668241</v>
+        <v>668353</v>
       </c>
       <c r="R12" t="n">
-        <v>6691789</v>
+        <v>6691720</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,70 +1879,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853668</t>
+          <t>https://artportalen.se/Sighting/128260556</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128260551</v>
+        <v>128344128</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668206</v>
+        <v>668138</v>
       </c>
       <c r="R13" t="n">
-        <v>6691675</v>
+        <v>6691627</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,11 +1967,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,73 +1981,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260551</t>
+          <t>https://artportalen.se/Sighting/128344128</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125855888</v>
+        <v>127382963</v>
       </c>
       <c r="B14" t="n">
-        <v>57141</v>
+        <v>93215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668226</v>
+        <v>668299</v>
       </c>
       <c r="R14" t="n">
-        <v>6691879</v>
+        <v>6691892</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2022,12 +2063,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,27 +2083,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855888</t>
+          <t>https://artportalen.se/Sighting/127382963</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125855890</v>
+        <v>128344126</v>
       </c>
       <c r="B15" t="n">
-        <v>57141</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,45 +2111,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668217</v>
+        <v>668368</v>
       </c>
       <c r="R15" t="n">
-        <v>6691903</v>
+        <v>6691735</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2132,12 +2165,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2152,27 +2185,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855890</t>
+          <t>https://artportalen.se/Sighting/128344126</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126056868</v>
+        <v>125807856</v>
       </c>
       <c r="B16" t="n">
-        <v>57141</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,39 +2213,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668245</v>
+        <v>668270</v>
       </c>
       <c r="R16" t="n">
-        <v>6691768</v>
+        <v>6691807</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2264,70 +2292,60 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126056868</t>
+          <t>https://artportalen.se/Sighting/125807856</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128260538</v>
+        <v>136824218</v>
       </c>
       <c r="B17" t="n">
-        <v>57141</v>
+        <v>75566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668254</v>
+        <v>668053</v>
       </c>
       <c r="R17" t="n">
-        <v>6691649</v>
+        <v>6691608</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2351,17 +2369,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fynd av stjärtfjäder</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,6 +2385,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2387,59 +2415,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260538</t>
+          <t>https://artportalen.se/Sighting/136824218</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132894822</v>
+        <v>128260536</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668208</v>
+        <v>668066</v>
       </c>
       <c r="R18" t="n">
-        <v>6691910</v>
+        <v>6691644</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2463,17 +2486,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,6 +2502,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2499,16 +2532,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894822</t>
+          <t>https://artportalen.se/Sighting/128260536</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132894823</v>
+        <v>125853668</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,42 +2549,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668214</v>
+        <v>668241</v>
       </c>
       <c r="R19" t="n">
-        <v>6691897</v>
+        <v>6691789</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2575,17 +2603,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2600,27 +2623,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894823</t>
+          <t>https://artportalen.se/Sighting/125853668</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132894824</v>
+        <v>128260551</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,42 +2651,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668286</v>
+        <v>668206</v>
       </c>
       <c r="R20" t="n">
-        <v>6691782</v>
+        <v>6691675</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2687,17 +2710,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,16 +2746,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894824</t>
+          <t>https://artportalen.se/Sighting/128260551</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132894825</v>
+        <v>136824216</v>
       </c>
       <c r="B21" t="n">
-        <v>57162</v>
+        <v>58005</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,42 +2763,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668297</v>
+        <v>668209</v>
       </c>
       <c r="R21" t="n">
-        <v>6691773</v>
+        <v>6691664</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2799,17 +2822,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,16 +2853,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894825</t>
+          <t>https://artportalen.se/Sighting/136824216</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132894826</v>
+        <v>125855888</v>
       </c>
       <c r="B22" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2870,24 +2888,27 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668314</v>
+        <v>668226</v>
       </c>
       <c r="R22" t="n">
-        <v>6691782</v>
+        <v>6691879</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2911,17 +2932,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,27 +2952,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894826</t>
+          <t>https://artportalen.se/Sighting/125855888</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132894832</v>
+        <v>125855890</v>
       </c>
       <c r="B23" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,24 +2998,27 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668308</v>
+        <v>668217</v>
       </c>
       <c r="R23" t="n">
-        <v>6691782</v>
+        <v>6691903</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3023,17 +3042,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3048,27 +3062,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894832</t>
+          <t>https://artportalen.se/Sighting/125855890</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132894833</v>
+        <v>126056868</v>
       </c>
       <c r="B24" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3101,14 +3115,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668319</v>
+        <v>668245</v>
       </c>
       <c r="R24" t="n">
-        <v>6691779</v>
+        <v>6691768</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3135,17 +3149,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3165,22 +3174,22 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894833</t>
+          <t>https://artportalen.se/Sighting/126056868</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128260591</v>
+        <v>128260538</v>
       </c>
       <c r="B25" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,43 +3197,44 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668209</v>
+        <v>668254</v>
       </c>
       <c r="R25" t="n">
-        <v>6691659</v>
+        <v>6691649</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3259,30 +3269,19 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fynd av stjärtfjäder</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3298,16 +3297,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260591</t>
+          <t>https://artportalen.se/Sighting/128260538</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125807887</v>
+        <v>132894822</v>
       </c>
       <c r="B26" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3315,34 +3314,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668279</v>
+        <v>668208</v>
       </c>
       <c r="R26" t="n">
-        <v>6691905</v>
+        <v>6691910</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3369,12 +3373,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3385,21 +3394,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3415,16 +3409,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807887</t>
+          <t>https://artportalen.se/Sighting/132894822</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125807888</v>
+        <v>132894823</v>
       </c>
       <c r="B27" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,34 +3426,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668255</v>
+        <v>668214</v>
       </c>
       <c r="R27" t="n">
-        <v>6691905</v>
+        <v>6691897</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3486,12 +3485,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,21 +3506,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3532,16 +3521,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807888</t>
+          <t>https://artportalen.se/Sighting/132894823</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125855910</v>
+        <v>132894824</v>
       </c>
       <c r="B28" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,37 +3538,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668295</v>
+        <v>668286</v>
       </c>
       <c r="R28" t="n">
-        <v>6691776</v>
+        <v>6691782</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3603,12 +3597,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3623,27 +3622,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855910</t>
+          <t>https://artportalen.se/Sighting/132894824</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125855912</v>
+        <v>132894825</v>
       </c>
       <c r="B29" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,37 +3650,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668276</v>
+        <v>668297</v>
       </c>
       <c r="R29" t="n">
-        <v>6691767</v>
+        <v>6691773</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3705,12 +3709,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3725,27 +3734,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855912</t>
+          <t>https://artportalen.se/Sighting/132894825</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125855913</v>
+        <v>132894826</v>
       </c>
       <c r="B30" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,37 +3762,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668200</v>
+        <v>668314</v>
       </c>
       <c r="R30" t="n">
-        <v>6691772</v>
+        <v>6691782</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3807,12 +3821,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3827,27 +3846,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855913</t>
+          <t>https://artportalen.se/Sighting/132894826</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127382960</v>
+        <v>132894832</v>
       </c>
       <c r="B31" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,34 +3874,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668228</v>
+        <v>668308</v>
       </c>
       <c r="R31" t="n">
-        <v>6691916</v>
+        <v>6691782</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3909,12 +3933,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3925,21 +3954,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3955,16 +3969,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382960</t>
+          <t>https://artportalen.se/Sighting/132894832</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128260579</v>
+        <v>132894833</v>
       </c>
       <c r="B32" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,37 +3986,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668356</v>
+        <v>668319</v>
       </c>
       <c r="R32" t="n">
-        <v>6691715</v>
+        <v>6691779</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4026,12 +4045,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,21 +4066,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4072,16 +4081,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260579</t>
+          <t>https://artportalen.se/Sighting/132894833</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125853673</v>
+        <v>128260591</v>
       </c>
       <c r="B33" t="n">
-        <v>99035</v>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4089,37 +4098,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668269</v>
+        <v>668209</v>
       </c>
       <c r="R33" t="n">
-        <v>6691918</v>
+        <v>6691659</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4143,12 +4161,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,33 +4175,49 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853673</t>
+          <t>https://artportalen.se/Sighting/128260591</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125855915</v>
+        <v>136824230</v>
       </c>
       <c r="B34" t="n">
-        <v>99035</v>
+        <v>5182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4191,37 +4225,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668328</v>
+        <v>668209</v>
       </c>
       <c r="R34" t="n">
-        <v>6691847</v>
+        <v>6691664</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,12 +4279,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4261,31 +4295,46 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855915</t>
+          <t>https://artportalen.se/Sighting/136824230</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125855916</v>
+        <v>136824844</v>
       </c>
       <c r="B35" t="n">
-        <v>99035</v>
+        <v>5182</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,37 +4342,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668198</v>
+        <v>668283</v>
       </c>
       <c r="R35" t="n">
-        <v>6691900</v>
+        <v>6691817</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4347,12 +4396,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4363,31 +4412,46 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855916</t>
+          <t>https://artportalen.se/Sighting/136824844</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125984242</v>
+        <v>125807887</v>
       </c>
       <c r="B36" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,21 +4459,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4419,13 +4483,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>667892</v>
+        <v>668279</v>
       </c>
       <c r="R36" t="n">
-        <v>6691648</v>
+        <v>6691905</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4465,31 +4529,46 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125984242</t>
+          <t>https://artportalen.se/Sighting/125807887</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128344141</v>
+        <v>125807888</v>
       </c>
       <c r="B37" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4497,37 +4576,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668248</v>
+        <v>668255</v>
       </c>
       <c r="R37" t="n">
-        <v>6691654</v>
+        <v>6691905</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4551,12 +4630,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4567,31 +4646,46 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344141</t>
+          <t>https://artportalen.se/Sighting/125807888</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125855908</v>
+        <v>125855910</v>
       </c>
       <c r="B38" t="n">
-        <v>106244</v>
+        <v>4781</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4599,21 +4693,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4623,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668294</v>
+        <v>668295</v>
       </c>
       <c r="R38" t="n">
-        <v>6691884</v>
+        <v>6691776</v>
       </c>
       <c r="S38" t="n">
         <v>12</v>
@@ -4684,7 +4778,1623 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/125855910</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125855912</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>668276</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6691767</v>
+      </c>
+      <c r="S39" t="n">
+        <v>12</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855912</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125855913</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>668200</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6691772</v>
+      </c>
+      <c r="S40" t="n">
+        <v>12</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855913</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127382960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>668228</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6691916</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382960</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128260579</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>668356</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6691715</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260579</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136824220</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>668057</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6691608</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824220</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136824221</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>668354</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6691795</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824221</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136824214</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>668083</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6691653</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824214</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136824815</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>668298</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6691703</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824815</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125853673</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>668269</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6691918</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva-Lena1 Rådberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva-Lena1 Rådberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853673</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125855915</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>668328</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6691847</v>
+      </c>
+      <c r="S48" t="n">
+        <v>12</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855915</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125855916</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6691900</v>
+      </c>
+      <c r="S49" t="n">
+        <v>12</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855916</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125984242</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>667892</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6691648</v>
+      </c>
+      <c r="S50" t="n">
+        <v>12</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johanna Sollén Mattsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Johanna Sollén Mattsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984242</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128344141</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>668248</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6691654</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344141</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125855908</v>
+      </c>
+      <c r="B52" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>668294</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6691884</v>
+      </c>
+      <c r="S52" t="n">
+        <v>12</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/125855908</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136824217</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92503</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>668216</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6691659</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824217</t>
         </is>
       </c>
     </row>
@@ -4727,6 +6437,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136824227</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136824228</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136824229</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>136824217</v>
       </c>
       <c r="B53" t="n">
-        <v>92503</v>
+        <v>92505</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136824222</v>
+        <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>83343</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,37 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668057</v>
+        <v>667842</v>
       </c>
       <c r="R6" t="n">
-        <v>6691608</v>
+        <v>6691599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,17 +1208,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal senvuxen gran med grov bark.</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1222,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1263,54 +1254,57 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824222</t>
+          <t>https://artportalen.se/Sighting/136974092</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128260561</v>
+        <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>91680</v>
+        <v>83343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>667956</v>
+        <v>668057</v>
       </c>
       <c r="R7" t="n">
-        <v>6691635</v>
+        <v>6691608</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,12 +1328,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal senvuxen gran med grov bark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,8 +1347,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1365,38 +1380,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260561</t>
+          <t>https://artportalen.se/Sighting/136824222</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136824227</v>
+        <v>128260561</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668027</v>
+        <v>667956</v>
       </c>
       <c r="R8" t="n">
-        <v>6691562</v>
+        <v>6691635</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,17 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar.</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,13 +1482,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824227</t>
+          <t>https://artportalen.se/Sighting/128260561</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136824228</v>
+        <v>136824227</v>
       </c>
       <c r="B9" t="n">
         <v>93411</v>
@@ -1513,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668033</v>
+        <v>668027</v>
       </c>
       <c r="R9" t="n">
-        <v>6691587</v>
+        <v>6691562</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,13 +1589,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824228</t>
+          <t>https://artportalen.se/Sighting/136824227</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136824229</v>
+        <v>136824228</v>
       </c>
       <c r="B10" t="n">
         <v>93411</v>
@@ -1620,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668276</v>
+        <v>668033</v>
       </c>
       <c r="R10" t="n">
-        <v>6691689</v>
+        <v>6691587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,16 +1696,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824229</t>
+          <t>https://artportalen.se/Sighting/136824228</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128260554</v>
+        <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1713,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,13 +1737,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668031</v>
+        <v>668276</v>
       </c>
       <c r="R11" t="n">
-        <v>6691632</v>
+        <v>6691689</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,12 +1767,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,16 +1803,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260554</t>
+          <t>https://artportalen.se/Sighting/136824229</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128260556</v>
+        <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668353</v>
+        <v>668037</v>
       </c>
       <c r="R12" t="n">
-        <v>6691720</v>
+        <v>6691586</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,12 +1874,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,16 +1905,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260556</t>
+          <t>https://artportalen.se/Sighting/136974119</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128344128</v>
+        <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,34 +1922,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668138</v>
+        <v>668037</v>
       </c>
       <c r="R13" t="n">
-        <v>6691627</v>
+        <v>6691617</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,12 +1976,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,27 +1996,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344128</t>
+          <t>https://artportalen.se/Sighting/136974122</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127382963</v>
+        <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93215</v>
+        <v>93411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2033,13 +2048,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668299</v>
+        <v>668044</v>
       </c>
       <c r="R14" t="n">
-        <v>6691892</v>
+        <v>6691566</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,12 +2078,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,51 +2109,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382963</t>
+          <t>https://artportalen.se/Sighting/136974123</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128344126</v>
+        <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>92869</v>
+        <v>93411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668368</v>
+        <v>668052</v>
       </c>
       <c r="R15" t="n">
-        <v>6691735</v>
+        <v>6691625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,12 +2180,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2185,65 +2200,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344126</t>
+          <t>https://artportalen.se/Sighting/136974124</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125807856</v>
+        <v>128260554</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>93209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668270</v>
+        <v>668031</v>
       </c>
       <c r="R16" t="n">
-        <v>6691807</v>
+        <v>6691632</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2267,12 +2282,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,16 +2313,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807856</t>
+          <t>https://artportalen.se/Sighting/128260554</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136824218</v>
+        <v>128260556</v>
       </c>
       <c r="B17" t="n">
-        <v>75566</v>
+        <v>93209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2339,13 +2354,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668053</v>
+        <v>668353</v>
       </c>
       <c r="R17" t="n">
-        <v>6691608</v>
+        <v>6691720</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2369,12 +2384,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,21 +2400,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2415,16 +2415,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824218</t>
+          <t>https://artportalen.se/Sighting/128260556</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128260536</v>
+        <v>128344128</v>
       </c>
       <c r="B18" t="n">
-        <v>79946</v>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,37 +2432,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668066</v>
+        <v>668138</v>
       </c>
       <c r="R18" t="n">
-        <v>6691644</v>
+        <v>6691627</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2502,84 +2502,69 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260536</t>
+          <t>https://artportalen.se/Sighting/128344128</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125853668</v>
+        <v>127382963</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>93215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>4368</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668241</v>
+        <v>668299</v>
       </c>
       <c r="R19" t="n">
-        <v>6691789</v>
+        <v>6691892</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2603,12 +2588,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,27 +2608,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853668</t>
+          <t>https://artportalen.se/Sighting/127382963</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128260551</v>
+        <v>128344126</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2651,42 +2636,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668206</v>
+        <v>668368</v>
       </c>
       <c r="R20" t="n">
-        <v>6691675</v>
+        <v>6691735</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2716,11 +2696,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,27 +2710,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260551</t>
+          <t>https://artportalen.se/Sighting/128344126</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136824216</v>
+        <v>125807856</v>
       </c>
       <c r="B21" t="n">
-        <v>58005</v>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,42 +2738,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668209</v>
+        <v>668270</v>
       </c>
       <c r="R21" t="n">
-        <v>6691664</v>
+        <v>6691807</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2822,12 +2792,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,62 +2823,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824216</t>
+          <t>https://artportalen.se/Sighting/125807856</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125855888</v>
+        <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>57141</v>
+        <v>93449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668226</v>
+        <v>668038</v>
       </c>
       <c r="R22" t="n">
-        <v>6691879</v>
+        <v>6691587</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2932,12 +2894,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,73 +2914,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855888</t>
+          <t>https://artportalen.se/Sighting/136974099</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125855890</v>
+        <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>57141</v>
+        <v>93449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668217</v>
+        <v>668038</v>
       </c>
       <c r="R23" t="n">
-        <v>6691903</v>
+        <v>6691565</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3042,12 +2996,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3062,70 +3016,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855890</t>
+          <t>https://artportalen.se/Sighting/136974100</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126056868</v>
+        <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>57141</v>
+        <v>79476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668245</v>
+        <v>668033</v>
       </c>
       <c r="R24" t="n">
-        <v>6691768</v>
+        <v>6691616</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,12 +3098,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3165,6 +3114,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3174,70 +3138,60 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126056868</t>
+          <t>https://artportalen.se/Sighting/136974112</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128260538</v>
+        <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>57141</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668254</v>
+        <v>668028</v>
       </c>
       <c r="R25" t="n">
-        <v>6691649</v>
+        <v>6691616</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3261,17 +3215,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fynd av stjärtfjäder</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,6 +3231,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3297,59 +3261,54 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260538</t>
+          <t>https://artportalen.se/Sighting/136974113</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132894822</v>
+        <v>136824218</v>
       </c>
       <c r="B26" t="n">
-        <v>57162</v>
+        <v>75566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668208</v>
+        <v>668053</v>
       </c>
       <c r="R26" t="n">
-        <v>6691910</v>
+        <v>6691608</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3373,17 +3332,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3394,6 +3348,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3409,59 +3378,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894822</t>
+          <t>https://artportalen.se/Sighting/136824218</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132894823</v>
+        <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>75566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668214</v>
+        <v>667774</v>
       </c>
       <c r="R27" t="n">
-        <v>6691897</v>
+        <v>6691616</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3485,17 +3449,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3506,6 +3465,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3521,59 +3495,54 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894823</t>
+          <t>https://artportalen.se/Sighting/136974105</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132894824</v>
+        <v>128260536</v>
       </c>
       <c r="B28" t="n">
-        <v>57162</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668286</v>
+        <v>668066</v>
       </c>
       <c r="R28" t="n">
-        <v>6691782</v>
+        <v>6691644</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3597,17 +3566,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3618,6 +3582,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3633,16 +3612,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894824</t>
+          <t>https://artportalen.se/Sighting/128260536</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132894825</v>
+        <v>125853668</v>
       </c>
       <c r="B29" t="n">
-        <v>57162</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,42 +3629,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668297</v>
+        <v>668241</v>
       </c>
       <c r="R29" t="n">
-        <v>6691773</v>
+        <v>6691789</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3709,17 +3683,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3734,27 +3703,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894825</t>
+          <t>https://artportalen.se/Sighting/125853668</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132894826</v>
+        <v>128260551</v>
       </c>
       <c r="B30" t="n">
-        <v>57162</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,42 +3731,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668314</v>
+        <v>668206</v>
       </c>
       <c r="R30" t="n">
-        <v>6691782</v>
+        <v>6691675</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3821,17 +3790,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3857,16 +3826,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894826</t>
+          <t>https://artportalen.se/Sighting/128260551</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132894832</v>
+        <v>136824216</v>
       </c>
       <c r="B31" t="n">
-        <v>57162</v>
+        <v>58005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3874,42 +3843,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668308</v>
+        <v>668209</v>
       </c>
       <c r="R31" t="n">
-        <v>6691782</v>
+        <v>6691664</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3933,17 +3902,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3969,16 +3933,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894832</t>
+          <t>https://artportalen.se/Sighting/136824216</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132894833</v>
+        <v>125855888</v>
       </c>
       <c r="B32" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4004,24 +3968,27 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668319</v>
+        <v>668226</v>
       </c>
       <c r="R32" t="n">
-        <v>6691779</v>
+        <v>6691879</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4045,17 +4012,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,27 +4032,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894833</t>
+          <t>https://artportalen.se/Sighting/125855888</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128260591</v>
+        <v>125855890</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4098,46 +4060,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668209</v>
+        <v>668217</v>
       </c>
       <c r="R33" t="n">
-        <v>6691659</v>
+        <v>6691903</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4161,12 +4122,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,49 +4136,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260591</t>
+          <t>https://artportalen.se/Sighting/125855890</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136824230</v>
+        <v>126056868</v>
       </c>
       <c r="B34" t="n">
-        <v>5182</v>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4225,37 +4170,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668209</v>
+        <v>668245</v>
       </c>
       <c r="R34" t="n">
-        <v>6691664</v>
+        <v>6691768</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4279,12 +4229,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4295,21 +4245,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4319,22 +4254,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824230</t>
+          <t>https://artportalen.se/Sighting/126056868</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136824844</v>
+        <v>128260538</v>
       </c>
       <c r="B35" t="n">
-        <v>5182</v>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4342,37 +4277,47 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668283</v>
+        <v>668254</v>
       </c>
       <c r="R35" t="n">
-        <v>6691817</v>
+        <v>6691649</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4396,12 +4341,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fynd av stjärtfjäder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4412,21 +4362,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4442,16 +4377,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824844</t>
+          <t>https://artportalen.se/Sighting/128260538</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125807887</v>
+        <v>132894822</v>
       </c>
       <c r="B36" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4459,34 +4394,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668279</v>
+        <v>668208</v>
       </c>
       <c r="R36" t="n">
-        <v>6691905</v>
+        <v>6691910</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4513,12 +4453,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4529,21 +4474,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4559,16 +4489,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807887</t>
+          <t>https://artportalen.se/Sighting/132894822</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125807888</v>
+        <v>132894823</v>
       </c>
       <c r="B37" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,34 +4506,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668255</v>
+        <v>668214</v>
       </c>
       <c r="R37" t="n">
-        <v>6691905</v>
+        <v>6691897</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4630,12 +4565,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4646,21 +4586,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4676,16 +4601,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807888</t>
+          <t>https://artportalen.se/Sighting/132894823</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125855910</v>
+        <v>132894824</v>
       </c>
       <c r="B38" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,37 +4618,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668295</v>
+        <v>668286</v>
       </c>
       <c r="R38" t="n">
-        <v>6691776</v>
+        <v>6691782</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4747,12 +4677,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4767,27 +4702,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855910</t>
+          <t>https://artportalen.se/Sighting/132894824</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125855912</v>
+        <v>132894825</v>
       </c>
       <c r="B39" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,37 +4730,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668276</v>
+        <v>668297</v>
       </c>
       <c r="R39" t="n">
-        <v>6691767</v>
+        <v>6691773</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4849,12 +4789,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4869,27 +4814,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855912</t>
+          <t>https://artportalen.se/Sighting/132894825</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125855913</v>
+        <v>132894826</v>
       </c>
       <c r="B40" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,37 +4842,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668200</v>
+        <v>668314</v>
       </c>
       <c r="R40" t="n">
-        <v>6691772</v>
+        <v>6691782</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4951,12 +4901,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4971,27 +4926,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855913</t>
+          <t>https://artportalen.se/Sighting/132894826</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127382960</v>
+        <v>132894832</v>
       </c>
       <c r="B41" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,34 +4954,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668228</v>
+        <v>668308</v>
       </c>
       <c r="R41" t="n">
-        <v>6691916</v>
+        <v>6691782</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5053,12 +5013,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5069,21 +5034,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5099,16 +5049,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382960</t>
+          <t>https://artportalen.se/Sighting/132894832</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128260579</v>
+        <v>132894833</v>
       </c>
       <c r="B42" t="n">
-        <v>4781</v>
+        <v>57162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5116,37 +5066,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668356</v>
+        <v>668319</v>
       </c>
       <c r="R42" t="n">
-        <v>6691715</v>
+        <v>6691779</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5170,12 +5125,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,21 +5146,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5216,16 +5161,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260579</t>
+          <t>https://artportalen.se/Sighting/132894833</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136824220</v>
+        <v>128260591</v>
       </c>
       <c r="B43" t="n">
-        <v>4783</v>
+        <v>5179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,37 +5178,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668057</v>
+        <v>668209</v>
       </c>
       <c r="R43" t="n">
-        <v>6691608</v>
+        <v>6691659</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5287,12 +5241,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,6 +5255,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5333,16 +5288,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824220</t>
+          <t>https://artportalen.se/Sighting/128260591</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136824221</v>
+        <v>136824230</v>
       </c>
       <c r="B44" t="n">
-        <v>4783</v>
+        <v>5182</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5350,21 +5305,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5374,10 +5329,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668354</v>
+        <v>668209</v>
       </c>
       <c r="R44" t="n">
-        <v>6691795</v>
+        <v>6691664</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5450,56 +5405,51 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824221</t>
+          <t>https://artportalen.se/Sighting/136824230</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136824214</v>
+        <v>136824844</v>
       </c>
       <c r="B45" t="n">
-        <v>58169</v>
+        <v>5182</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668083</v>
+        <v>668283</v>
       </c>
       <c r="R45" t="n">
-        <v>6691653</v>
+        <v>6691817</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5543,6 +5493,21 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
@@ -5557,59 +5522,54 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824214</t>
+          <t>https://artportalen.se/Sighting/136824844</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136824815</v>
+        <v>125807887</v>
       </c>
       <c r="B46" t="n">
-        <v>58169</v>
+        <v>4781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668298</v>
+        <v>668279</v>
       </c>
       <c r="R46" t="n">
-        <v>6691703</v>
+        <v>6691905</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5633,12 +5593,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5649,6 +5609,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5664,16 +5639,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824815</t>
+          <t>https://artportalen.se/Sighting/125807887</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125853673</v>
+        <v>125807888</v>
       </c>
       <c r="B47" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5681,37 +5656,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668269</v>
+        <v>668255</v>
       </c>
       <c r="R47" t="n">
-        <v>6691918</v>
+        <v>6691905</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5751,31 +5726,46 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853673</t>
+          <t>https://artportalen.se/Sighting/125807888</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125855915</v>
+        <v>125855910</v>
       </c>
       <c r="B48" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5783,21 +5773,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5807,10 +5797,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668328</v>
+        <v>668295</v>
       </c>
       <c r="R48" t="n">
-        <v>6691847</v>
+        <v>6691776</v>
       </c>
       <c r="S48" t="n">
         <v>12</v>
@@ -5868,16 +5858,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855915</t>
+          <t>https://artportalen.se/Sighting/125855910</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125855916</v>
+        <v>125855912</v>
       </c>
       <c r="B49" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5885,21 +5875,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5909,10 +5899,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668198</v>
+        <v>668276</v>
       </c>
       <c r="R49" t="n">
-        <v>6691900</v>
+        <v>6691767</v>
       </c>
       <c r="S49" t="n">
         <v>12</v>
@@ -5970,16 +5960,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855916</t>
+          <t>https://artportalen.se/Sighting/125855912</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125984242</v>
+        <v>125855913</v>
       </c>
       <c r="B50" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,21 +5977,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6011,10 +6001,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>667892</v>
+        <v>668200</v>
       </c>
       <c r="R50" t="n">
-        <v>6691648</v>
+        <v>6691772</v>
       </c>
       <c r="S50" t="n">
         <v>12</v>
@@ -6061,27 +6051,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125984242</t>
+          <t>https://artportalen.se/Sighting/125855913</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128344141</v>
+        <v>127382960</v>
       </c>
       <c r="B51" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,37 +6079,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668248</v>
+        <v>668228</v>
       </c>
       <c r="R51" t="n">
-        <v>6691654</v>
+        <v>6691916</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6143,12 +6133,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6159,31 +6149,46 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344141</t>
+          <t>https://artportalen.se/Sighting/127382960</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125855908</v>
+        <v>128260579</v>
       </c>
       <c r="B52" t="n">
-        <v>106244</v>
+        <v>4781</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6191,37 +6196,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668294</v>
+        <v>668356</v>
       </c>
       <c r="R52" t="n">
-        <v>6691884</v>
+        <v>6691715</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6245,12 +6250,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6261,53 +6266,68 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855908</t>
+          <t>https://artportalen.se/Sighting/128260579</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136824217</v>
+        <v>136824220</v>
       </c>
       <c r="B53" t="n">
-        <v>92505</v>
+        <v>4783</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>102306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6317,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668216</v>
+        <v>668057</v>
       </c>
       <c r="R53" t="n">
-        <v>6691659</v>
+        <v>6691608</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6361,7 +6381,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6393,6 +6412,1281 @@
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824220</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136824221</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>668354</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6691795</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824221</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136824214</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>668083</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6691653</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824214</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136824815</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>668298</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6691703</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824815</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136974093</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>667852</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6691618</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136974093</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136974094</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>668079</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6691638</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136974094</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125853673</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>668269</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6691918</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Eva-Lena1 Rådberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Eva-Lena1 Rådberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853673</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125855915</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>668328</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6691847</v>
+      </c>
+      <c r="S60" t="n">
+        <v>12</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855915</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125855916</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6691900</v>
+      </c>
+      <c r="S61" t="n">
+        <v>12</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855916</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125984242</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>667892</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6691648</v>
+      </c>
+      <c r="S62" t="n">
+        <v>12</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Johanna Sollén Mattsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Johanna Sollén Mattsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984242</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128344141</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>668248</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6691654</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344141</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125855908</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>668294</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6691884</v>
+      </c>
+      <c r="S64" t="n">
+        <v>12</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855908</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136824217</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92505</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>668216</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6691659</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136824217</t>
         </is>
@@ -6452,6 +7746,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92505</v>
+        <v>92507</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92507</v>
+        <v>92509</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92510</v>
+        <v>92516</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92516</v>
+        <v>92520</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136824218</v>
       </c>
       <c r="B26" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>136824216</v>
       </c>
       <c r="B31" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>136824214</v>
       </c>
       <c r="B55" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136824815</v>
       </c>
       <c r="B56" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>136974093</v>
       </c>
       <c r="B57" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>136974094</v>
       </c>
       <c r="B58" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92522</v>
+        <v>92535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136824218</v>
       </c>
       <c r="B26" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>136824216</v>
       </c>
       <c r="B31" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3861,11 +3861,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
@@ -6539,7 +6535,7 @@
         <v>136824214</v>
       </c>
       <c r="B55" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6565,11 +6561,7 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
@@ -6646,7 +6638,7 @@
         <v>136824815</v>
       </c>
       <c r="B56" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6672,11 +6664,7 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
@@ -6753,7 +6741,7 @@
         <v>136974093</v>
       </c>
       <c r="B57" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,11 +6767,7 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
@@ -6860,7 +6844,7 @@
         <v>136974094</v>
       </c>
       <c r="B58" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6886,11 +6870,7 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
@@ -7579,7 +7559,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92535</v>
+        <v>92537</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92537</v>
+        <v>92540</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136824218</v>
       </c>
       <c r="B26" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>136824216</v>
       </c>
       <c r="B31" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>136824230</v>
       </c>
       <c r="B44" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>136824844</v>
       </c>
       <c r="B45" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136824220</v>
       </c>
       <c r="B53" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>136824221</v>
       </c>
       <c r="B54" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136824214</v>
       </c>
       <c r="B55" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>136824815</v>
       </c>
       <c r="B56" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136974093</v>
       </c>
       <c r="B57" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136974094</v>
       </c>
       <c r="B58" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92540</v>
+        <v>92550</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136824218</v>
       </c>
       <c r="B26" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>136824216</v>
       </c>
       <c r="B31" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136824214</v>
       </c>
       <c r="B55" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>136824815</v>
       </c>
       <c r="B56" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136974093</v>
       </c>
       <c r="B57" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136974094</v>
       </c>
       <c r="B58" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92551</v>
+        <v>92554</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136824213</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136824809</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136824222</v>
       </c>
       <c r="B7" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136824227</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>136824228</v>
       </c>
       <c r="B10" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136824229</v>
       </c>
       <c r="B11" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136824218</v>
       </c>
       <c r="B26" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>136824216</v>
       </c>
       <c r="B31" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136824214</v>
       </c>
       <c r="B55" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>136824815</v>
       </c>
       <c r="B56" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136974093</v>
       </c>
       <c r="B57" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136974094</v>
       </c>
       <c r="B58" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136824217</v>
       </c>
       <c r="B65" t="n">
-        <v>92556</v>
+        <v>92561</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>75610</v>
+        <v>75611</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>136974092</v>
       </c>
       <c r="B6" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136974119</v>
       </c>
       <c r="B12" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136974122</v>
       </c>
       <c r="B13" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136974123</v>
       </c>
       <c r="B14" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136974124</v>
       </c>
       <c r="B15" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136974099</v>
       </c>
       <c r="B22" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136974100</v>
       </c>
       <c r="B23" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136974112</v>
       </c>
       <c r="B24" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136974113</v>
       </c>
       <c r="B25" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>136974105</v>
       </c>
       <c r="B27" t="n">
-        <v>75611</v>
+        <v>75614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136974093</v>
       </c>
       <c r="B57" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136974094</v>
       </c>
       <c r="B58" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
